--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487835_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487835_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.057</v>
+        <v>6.1157</v>
       </c>
       <c r="E2" t="n">
         <v>7.4927</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4357</v>
+        <v>-1.377</v>
       </c>
       <c r="G2" t="n">
         <v>6.1975</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1539</v>
+        <v>0.2127</v>
       </c>
       <c r="T2" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2225</v>
+        <v>0.2812</v>
       </c>
       <c r="V2" t="n">
         <v>-1.7513</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8014</v>
+        <v>0.768</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6462</v>
+        <v>-0.2111</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1552</v>
+        <v>0.979</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6686</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6375</v>
+        <v>0.6041</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1025</v>
+        <v>0.2453</v>
       </c>
       <c r="U3" t="n">
-        <v>0.535</v>
+        <v>0.3588</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0786</v>
+        <v>-0.4777</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.441</v>
+        <v>-0.7625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5196</v>
+        <v>0.2847</v>
       </c>
       <c r="G4" t="n">
         <v>1.4085</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2102</v>
+        <v>0.6539</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3882</v>
+        <v>0.0667</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2914</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.6621</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4905</v>
+        <v>-0.3834</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3668</v>
+        <v>-0.2788</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6337</v>
@@ -844,13 +844,13 @@
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0998</v>
+        <v>0.0954</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.199</v>
+        <v>-0.0919</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0992</v>
+        <v>0.1873</v>
       </c>
       <c r="V5" t="n">
         <v>0.4599</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2574</v>
+        <v>-1.9653</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.0862</v>
+        <v>-3.7648</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8288</v>
+        <v>1.7995</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1972</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0196</v>
+        <v>0.2725</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3262</v>
+        <v>-0.0047</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3066</v>
+        <v>0.2773</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6138</v>
+        <v>-2.4582</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5155</v>
+        <v>-2.3011</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0983</v>
+        <v>-0.1571</v>
       </c>
       <c r="G7" t="n">
         <v>-3.0343</v>
@@ -1000,13 +1000,13 @@
         <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0261</v>
+        <v>0.1817</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.261</v>
+        <v>-0.0467</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2871</v>
+        <v>0.2284</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0578</v>
+        <v>-2.7054</v>
       </c>
       <c r="E8" t="n">
         <v>0.4146</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4723</v>
+        <v>-3.12</v>
       </c>
       <c r="G8" t="n">
         <v>-3.2055</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1228</v>
+        <v>-0.7705</v>
       </c>
       <c r="T8" t="n">
         <v>-0.7862</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3366</v>
+        <v>0.0157</v>
       </c>
       <c r="V8" t="n">
         <v>0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4615</v>
+        <v>-4.071</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1482</v>
+        <v>-1.9338</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3133</v>
+        <v>-2.1371</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7335</v>
@@ -1156,13 +1156,13 @@
         <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0817</v>
+        <v>-0.6912</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9134</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1683</v>
+        <v>0.0078</v>
       </c>
       <c r="V9" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.2808</v>
+        <v>-6.4276</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9563</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.3244</v>
+        <v>-5.4712</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6952</v>
@@ -1234,13 +1234,13 @@
         <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.7542</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5905</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0169</v>
+        <v>-0.1637</v>
       </c>
       <c r="V10" t="n">
         <v>0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9722</v>
+        <v>-6.4849</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5284</v>
+        <v>-3.0997</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4438</v>
+        <v>-3.3851</v>
       </c>
       <c r="G11" t="n">
         <v>-6.0203</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5762</v>
+        <v>-1.0889</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3701</v>
+        <v>-0.9415</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2061</v>
+        <v>-0.1474</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7682</v>
+        <v>-7.9635</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5987</v>
+        <v>-2.7058</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.1696</v>
+        <v>-5.2577</v>
       </c>
       <c r="G12" t="n">
         <v>-5.9111</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2297</v>
+        <v>-0.4249</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3948</v>
+        <v>-0.5019</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1651</v>
+        <v>0.077</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6275</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.3321</v>
+        <v>-26.332</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.211300000000001</v>
+        <v>-8.2112</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.1206</v>
+        <v>-18.1208</v>
       </c>
       <c r="G13" t="n">
         <v>-22.4934</v>
@@ -1468,13 +1468,13 @@
         <v>11.4466</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.709500000000001</v>
+        <v>-1.7094</v>
       </c>
       <c r="T13" t="n">
         <v>-3.419</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7097</v>
+        <v>1.7096</v>
       </c>
       <c r="V13" t="n">
         <v>-4.2103</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.7401</v>
+        <v>8.155900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9299</v>
+        <v>6.287</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8102</v>
+        <v>1.8689</v>
       </c>
       <c r="G14" t="n">
         <v>3.4125</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2631</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7763</v>
+        <v>0.1334</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4868</v>
+        <v>0.5455</v>
       </c>
       <c r="V14" t="n">
         <v>3.8564</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4921</v>
+        <v>6.4319</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5126</v>
+        <v>4.834</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9795</v>
+        <v>1.5979</v>
       </c>
       <c r="G15" t="n">
         <v>5.808</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4541</v>
+        <v>0.3939</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7177</v>
+        <v>-0.3962</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1718</v>
+        <v>0.7901</v>
       </c>
       <c r="V15" t="n">
         <v>0.23</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9216</v>
+        <v>5.2343</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0478</v>
+        <v>4.155</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8738</v>
+        <v>1.0793</v>
       </c>
       <c r="G16" t="n">
         <v>4.4062</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8383</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2511</v>
+        <v>-0.0456</v>
       </c>
       <c r="V16" t="n">
         <v>0.9376</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8801</v>
+        <v>3.1798</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7683</v>
+        <v>3.1651</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1118</v>
+        <v>0.0147</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5706</v>
+        <v>2.9206</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7183</v>
+        <v>3.6375</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8524</v>
+        <v>-0.7168</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2974</v>
+        <v>3.3004</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3469</v>
+        <v>2.7395</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9504</v>
+        <v>0.5609</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7267</v>
+        <v>-0.3797</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3713</v>
+        <v>0.898</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0981</v>
+        <v>-1.2777</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6394</v>
+        <v>0.3861</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2577</v>
+        <v>-0.1352</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3817</v>
+        <v>0.5213</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3351</v>
+        <v>-1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5941</v>
+        <v>2.9491</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8437</v>
+        <v>1.6612</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2496</v>
+        <v>1.288</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9206</v>
+        <v>1.5706</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6375</v>
+        <v>0.7183</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7168</v>
+        <v>0.8524</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3004</v>
+        <v>2.2974</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7395</v>
+        <v>0.3469</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5609</v>
+        <v>1.9504</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3797</v>
+        <v>-0.7267</v>
       </c>
       <c r="N18" t="n">
-        <v>0.898</v>
+        <v>0.3713</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2777</v>
+        <v>-1.0981</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0406</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1996</v>
+        <v>0.7084</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4567</v>
+        <v>0.1505</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2571</v>
+        <v>0.5579</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1675</v>
+        <v>2.3351</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8342</v>
+        <v>1.8635</v>
       </c>
       <c r="E19" t="n">
         <v>1.1126</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7216</v>
+        <v>0.7509</v>
       </c>
       <c r="G19" t="n">
         <v>1.1684</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V19" t="n">
         <v>0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6361</v>
+        <v>1.3235</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8492</v>
+        <v>2.742</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.213</v>
+        <v>-1.4185</v>
       </c>
       <c r="G20" t="n">
         <v>3.0178</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9721</v>
+        <v>0.6595</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1924</v>
+        <v>0.0853</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.5742</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5213</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5268</v>
+        <v>1.3213</v>
       </c>
       <c r="E21" t="n">
         <v>-0.4004</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9272</v>
+        <v>1.7217</v>
       </c>
       <c r="G21" t="n">
         <v>0.8809</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2297</v>
+        <v>0.0242</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3504</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9285</v>
+        <v>-0.704</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.485</v>
+        <v>-1.3779</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5565</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0.3632</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4156</v>
+        <v>-0.191</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0241</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2961</v>
+        <v>-1.2667</v>
       </c>
       <c r="E23" t="n">
         <v>-2.2117</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9156</v>
+        <v>0.945</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0327</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4091</v>
+        <v>-0.3797</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0828</v>
+        <v>-0.0535</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0687</v>
+        <v>-2.1567</v>
       </c>
       <c r="E24" t="n">
         <v>-1.8463</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2224</v>
+        <v>-0.3105</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0222</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0059</v>
+        <v>-0.0939</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1246</v>
+        <v>0.0365</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.3318</v>
+        <v>26.3319</v>
       </c>
       <c r="E25" t="n">
-        <v>18.1207</v>
+        <v>18.1206</v>
       </c>
       <c r="F25" t="n">
-        <v>8.211199999999998</v>
+        <v>8.211300000000001</v>
       </c>
       <c r="G25" t="n">
         <v>22.4933</v>
@@ -2386,7 +2386,7 @@
         <v>12.981</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8582</v>
+        <v>-0.8582000000000002</v>
       </c>
       <c r="N25" t="n">
         <v>3.0197</v>
@@ -2404,13 +2404,13 @@
         <v>9.365399999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7095</v>
+        <v>1.7096</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.7096</v>
+        <v>-1.7094</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4192</v>
+        <v>3.419</v>
       </c>
       <c r="V25" t="n">
         <v>4.2104</v>
